--- a/AAAGameData/DataTables/LayerTable.xlsx
+++ b/AAAGameData/DataTables/LayerTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -77,7 +77,7 @@
     <t>4,4,4</t>
   </si>
   <si>
-    <t>0.5,0.5,0.5</t>
+    <t>0,0,0</t>
   </si>
   <si>
     <t>[-3,3,0],[-3,1.5,0],[-3,0,0]</t>
@@ -89,9 +89,6 @@
     <t>3,3,3</t>
   </si>
   <si>
-    <t>0,0,0</t>
-  </si>
-  <si>
     <t>[-2,3,0],[-2,1.5,0],[-2,0,0]</t>
   </si>
   <si>
@@ -104,7 +101,7 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>[-1,1.5,0],[-1,0,0]</t>
+    <t>[-1,2.25,0],[-1,0.75,0]</t>
   </si>
 </sst>
 </file>
@@ -1362,10 +1359,10 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
         <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="2:6">
@@ -1373,16 +1370,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/LayerTable.xlsx
+++ b/AAAGameData/DataTables/LayerTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>#</t>
   </si>
@@ -38,22 +38,10 @@
     <t>ID</t>
   </si>
   <si>
-    <t>CatNum</t>
-  </si>
-  <si>
-    <t>RowGap</t>
-  </si>
-  <si>
-    <t>StartPos</t>
+    <t>PosArr</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>float[]</t>
   </si>
   <si>
     <t>Vector3[]</t>
@@ -62,43 +50,22 @@
     <t>备注</t>
   </si>
   <si>
-    <t>各层每行小猫数量，4,4,4表示该层有三行，每行4只小猫</t>
-  </si>
-  <si>
-    <t>每行小猫间距</t>
-  </si>
-  <si>
-    <t>每行小猫起始位置</t>
+    <t>每层所有小猫的位置</t>
   </si>
   <si>
     <t>第1种层配置</t>
   </si>
   <si>
-    <t>4,4,4</t>
-  </si>
-  <si>
-    <t>0,0,0</t>
-  </si>
-  <si>
-    <t>[-3,3,0],[-3,1.5,0],[-3,0,0]</t>
+    <t>[-3,3,0],[-3,1.5,0],[-3,0,0],[-3,-1.5,0],[-3,-3,0],[-1.5,3,0],[-1.5,1.5,0],[-1.5,0,0],[-1.5,-1.5,0],[-1.5,-3,0]</t>
   </si>
   <si>
     <t>第2种层配置</t>
-  </si>
-  <si>
-    <t>3,3,3</t>
   </si>
   <si>
     <t>[-2,3,0],[-2,1.5,0],[-2,0,0]</t>
   </si>
   <si>
     <t>第3种层配置</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>0,0</t>
   </si>
   <si>
     <t>[-1,2.25,0],[-1,0.75,0]</t>
@@ -1263,13 +1230,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="23.0909090909091" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="51.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="51.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1280,7 +1245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1290,107 +1255,71 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:4">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="2:6">
+    <row r="6" customFormat="1" spans="2:4">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="2:6">
+    <row r="7" customFormat="1" spans="2:4">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="D1:X1">
+    <dataValidation type="list" allowBlank="1" sqref="D1:V1">
       <formula1>"i18n"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D3:F3">
+    <dataValidation type="list" sqref="D3">
       <formula1>"int,bool,enum,double,string[],string,float,uint,short,Vector4,Vector2,Vector3Int,Vector3,Color,Color32,Vector3[],Vector2Int,int[],float[],bool[],double[],ushort,ulong,int[][],double[][],decimal,long,float[][],bool[][],Rect,Quaternion,DateTime,sbyte,char"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G3:X3">
+    <dataValidation type="list" sqref="E3:V3">
       <formula1>"double,int,bool,string,float,enum,string[],uint,short,Vector2[],Vector3Int[],int4[],int4,Vector3Int,Vector3,Vector4[],Vector2,Vector4,Color,Color32,Vector2Int,Vector3[],Vector2Int[],Type,long[],bool[],int[],float[],double[],float[][],decimal,double[][]"</formula1>
     </dataValidation>
   </dataValidations>

--- a/AAAGameData/DataTables/LayerTable.xlsx
+++ b/AAAGameData/DataTables/LayerTable.xlsx
@@ -56,7 +56,7 @@
     <t>第1种层配置</t>
   </si>
   <si>
-    <t>[-3,3,0],[-3,1.5,0],[-3,0,0],[-3,-1.5,0],[-3,-3,0],[-1.5,3,0],[-1.5,1.5,0],[-1.5,0,0],[-1.5,-1.5,0],[-1.5,-3,0]</t>
+    <t>[-3,3,0],[-3,1.5,0],[-3,0,0],[-3,-1.5,0],[-3,-3,0],[-1.5,3,0],[-1.5,1.5,0],[-1.5,0,0],[-1.5,-1.5,0],[0,-3,0],[0,3,0],[0,1.5,0],[0,0,0],[0,-1.5,0],[1.5,3,0],[1.5,1.5,0],[1.5,0,0],[1.5,-1.5,0],[1.5,-3,0]</t>
   </si>
   <si>
     <t>第2种层配置</t>
@@ -1234,7 +1234,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="51.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="89.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">

--- a/AAAGameData/DataTables/LayerTable.xlsx
+++ b/AAAGameData/DataTables/LayerTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>#</t>
   </si>
@@ -41,6 +41,9 @@
     <t>PosArr</t>
   </si>
   <si>
+    <t>LayerCount</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -53,22 +56,25 @@
     <t>每层所有小猫的位置</t>
   </si>
   <si>
+    <t>每层小猫数量</t>
+  </si>
+  <si>
     <t>第1种层配置</t>
   </si>
   <si>
-    <t>[-3,3,0],[-3,1.5,0],[-3,0,0],[-3,-1.5,0],[-3,-3,0],[-1.5,3,0],[-1.5,1.5,0],[-1.5,0,0],[-1.5,-1.5,0],[0,-3,0],[0,3,0],[0,1.5,0],[0,0,0],[0,-1.5,0],[1.5,3,0],[1.5,1.5,0],[1.5,0,0],[1.5,-1.5,0],[1.5,-3,0]</t>
+    <t>[-3,3,0],[-3,1.5,0],[-3,0,0],[-3,-1.5,0],[-3,-3,0],[-1.5,3,0],[-1.5,1.5,0],[-1.5,0,0],[-1.5,-1.5,0],[-1.5,-3,0],[0,-3,0],[0,3,0],[0,1.5,0],[0,0,0],[0,-1.5,0],[1.5,3,0],[1.5,1.5,0],[1.5,0,0],[1.5,-1.5,0],[1.5,-3,0]</t>
   </si>
   <si>
     <t>第2种层配置</t>
   </si>
   <si>
-    <t>[-2,3,0],[-2,1.5,0],[-2,0,0]</t>
+    <t>[-2,3,0],[-2,1.5,0],[-2,0,0],[-2,-1.5,0]</t>
   </si>
   <si>
     <t>第3种层配置</t>
   </si>
   <si>
-    <t>[-1,2.25,0],[-1,0.75,0]</t>
+    <t>[-1,2.25,0],[-1,0.75,0],[-1,-0.75,0]</t>
   </si>
 </sst>
 </file>
@@ -1230,11 +1236,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="89.0909090909091" customWidth="1"/>
+    <col min="4" max="4" width="161.545454545455" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1245,7 +1252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1255,61 +1262,139 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="2:4">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3">
+        <f>LEN(D5)-LEN(SUBSTITUTE(D5,"[",""))</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="2:5">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="2:4">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3">
+        <f>LEN(D6)-LEN(SUBSTITUTE(D6,"[",""))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="2:5">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="E7" s="3">
+        <f>LEN(D7)-LEN(SUBSTITUTE(D7,"[",""))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="5:5">
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="5:5">
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="5:5">
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="5:5">
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="5:5">
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="5:5">
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="5:5">
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="5:5">
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="5:5">
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="5:5">
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="5:5">
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="5:5">
+      <c r="E26" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/AAAGameData/DataTables/LayerTable.xlsx
+++ b/AAAGameData/DataTables/LayerTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>#</t>
   </si>
@@ -59,22 +59,322 @@
     <t>每层小猫数量</t>
   </si>
   <si>
-    <t>第1种层配置</t>
-  </si>
-  <si>
-    <t>[-3,3,0],[-3,1.5,0],[-3,0,0],[-3,-1.5,0],[-3,-3,0],[-1.5,3,0],[-1.5,1.5,0],[-1.5,0,0],[-1.5,-1.5,0],[-1.5,-3,0],[0,-3,0],[0,3,0],[0,1.5,0],[0,0,0],[0,-1.5,0],[1.5,3,0],[1.5,1.5,0],[1.5,0,0],[1.5,-1.5,0],[1.5,-3,0]</t>
-  </si>
-  <si>
-    <t>第2种层配置</t>
-  </si>
-  <si>
-    <t>[-2,3,0],[-2,1.5,0],[-2,0,0],[-2,-1.5,0]</t>
-  </si>
-  <si>
-    <t>第3种层配置</t>
-  </si>
-  <si>
-    <t>[-1,2.25,0],[-1,0.75,0],[-1,-0.75,0]</t>
+    <t>完整层（行排列）</t>
+  </si>
+  <si>
+    <t>[-3,3,0],[-1.5,3,0],[0,3,0],[1.5,3,0],[3,3,0],[-3,1.5,0],[-1.5,1.5,0],[0,1.5,0],[1.5,1.5,0],[3,1.5,0],[-3,0,0],[-1.5,0,0],[0,0,0],[1.5,0,0],[3,0,0],[-3,-1.5,0],[-1.5,-1.5,0],[0,-1.5,0],[1.5,-1.5,0],[3,-1.5,0],[-3,-3,0],[-1.5,-3,0],[0,-3,0],[1.5,-3,0],[3,-3,0]</t>
+  </si>
+  <si>
+    <t>完整行，第1行</t>
+  </si>
+  <si>
+    <t>[-3,3,0],[-1.5,3,0],[0,3,0],[1.5,3,0],[3,3,0]</t>
+  </si>
+  <si>
+    <t>完整行，第2行</t>
+  </si>
+  <si>
+    <t>[-3,1.5,0],[-1.5,1.5,0],[0,1.5,0],[1.5,1.5,0],[3,1.5,0]</t>
+  </si>
+  <si>
+    <t>完整行，第3行</t>
+  </si>
+  <si>
+    <t>[-3,0,0],[-1.5,0,0],[0,0,0],[1.5,0,0],[3,0,0]</t>
+  </si>
+  <si>
+    <t>完整行，第4行</t>
+  </si>
+  <si>
+    <t>[-3,-1.5,0],[-1.5,-1.5,0],[0,-1.5,0],[1.5,-1.5,0],[3,-1.5,0]</t>
+  </si>
+  <si>
+    <t>完整行，第5行</t>
+  </si>
+  <si>
+    <t>[-3,-3,0],[-1.5,-3,0],[0,-3,0],[1.5,-3,0],[3,-3,0]</t>
+  </si>
+  <si>
+    <t>完整列，第1列</t>
+  </si>
+  <si>
+    <t>[-3,3,0],[-3,1.5,0],[-3,0,0],[-3,-1.5,0],[-3,-3,0]</t>
+  </si>
+  <si>
+    <t>完整列，第2列</t>
+  </si>
+  <si>
+    <t>[-1.5,3,0],[-1.5,1.5,0],[-1.5,0,0],[-1.5,-1.5,0],[-1.5,-3,0]</t>
+  </si>
+  <si>
+    <t>完整列，第3列</t>
+  </si>
+  <si>
+    <t>[0,-3,0],[0,3,0],[0,1.5,0],[0,0,0],[0,-1.5,0]</t>
+  </si>
+  <si>
+    <t>完整列，第4列</t>
+  </si>
+  <si>
+    <t>[1.5,3,0],[1.5,1.5,0],[1.5,0,0],[1.5,-1.5,0],[1.5,-3,0]</t>
+  </si>
+  <si>
+    <t>完整列，第5列</t>
+  </si>
+  <si>
+    <t>[3,3,0],[3,1.5,0],[3,0,0],[3,-1.5,0],[3,-3,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，完成层</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,3,0],[-0.75,3,0],[0.75,3,0],[2.25,3,0],[-2.25,1.5,0],[-0.75,1.5,0],[0.75,1.5,0],[2.25,1.5,0],[-2.25,0,0],[-0.75,0,0],[0.75,0,0],[2.25,0,0],[-2.25,-1.5,0],[-0.75,-1.5,0],[0.75,-1.5,0],[2.25,-1.5,0],[-2.25,-3,0],[-0.75,-3,0],[0.75,-3,0],[2.25,-3,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第1行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,3,0],[-0.75,3,0],[0.75,3,0],[2.25,3,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第2行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,1.5,0],[-0.75,1.5,0],[0.75,1.5,0],[2.25,1.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第3行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,0,0],[-0.75,0,0],[0.75,0,0],[2.25,0,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第4行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,-1.5,0],[-0.75,-1.5,0],[0.75,-1.5,0],[2.25,-1.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第5行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,-3,0],[-0.75,-3,0],[0.75,-3,0],[2.25,-3,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x/y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，完整层</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,2.25,0],[-0.75,2.25,0],[0.75,2.25,0],[2.25,2.25,0],[-2.25,0.75,0],[-0.75,0.75,0],[0.75,0.75,0],[2.25,0.75,0],[-2.25,-0.75,0],[-0.75,-0.75,0],[0.75,-0.75,0],[2.25,-0.75,0],[-2.25,-2.25,0],[-0.75,-2.25,0],[0.75,-2.25,0],[2.25,-2.25,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x/y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,2.25,0],[-0.75,2.25,0],[0.75,2.25,0],[2.25,2.25,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x/y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,0.75,0],[-0.75,0.75,0],[0.75,0.75,0],[2.25,0.75,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x/y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,-0.75,0],[-0.75,-0.75,0],[0.75,-0.75,0],[2.25,-0.75,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x/y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.25,-2.25,0],[-0.75,-2.25,0],[0.75,-2.25,0],[2.25,-2.25,0]</t>
+  </si>
+  <si>
+    <t>居中十字</t>
+  </si>
+  <si>
+    <t>[-3,0,0],[-1.5,0,0],[0,0,0],[1.5,0,0],[3,0,0],[0,-3,0],[0,3,0],[0,1.5,0],[0,-1.5,0]</t>
+  </si>
+  <si>
+    <t>双对角线</t>
+  </si>
+  <si>
+    <t>[-3,3,0],[3,3,0],[-1.5,1.5,0],[1.5,1.5,0],[0,0,0],[-1.5,-1.5,0],[1.5,-1.5,0],[-3,-3,0],[3,-3,0]</t>
   </si>
 </sst>
 </file>
@@ -698,11 +998,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1236,11 +1537,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="161.545454545455" customWidth="1"/>
+    <col min="3" max="3" width="18.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="189" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1306,7 +1607,7 @@
       </c>
       <c r="E5" s="3">
         <f>LEN(D5)-LEN(SUBSTITUTE(D5,"[",""))</f>
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="2:5">
@@ -1321,7 +1622,7 @@
       </c>
       <c r="E6" s="3">
         <f>LEN(D6)-LEN(SUBSTITUTE(D6,"[",""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="2:5">
@@ -1336,65 +1637,398 @@
       </c>
       <c r="E7" s="3">
         <f>LEN(D7)-LEN(SUBSTITUTE(D7,"[",""))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="5:5">
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="5:5">
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="5:5">
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="5:5">
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="5:5">
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="5:5">
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="5:5">
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="5:5">
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="5:5">
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="5:5">
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="5:5">
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="5:5">
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="5:5">
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="5:5">
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="5:5">
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="5:5">
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="5:5">
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="5:5">
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="5:5">
-      <c r="E26" s="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" ref="E8:E15" si="0">LEN(D8)-LEN(SUBSTITUTE(D8,"[",""))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" ref="E16:E24" si="1">LEN(D16)-LEN(SUBSTITUTE(D16,"[",""))</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22">
+        <v>18</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="3">
+        <f>LEN(D22)-LEN(SUBSTITUTE(D22,"[",""))</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23">
+        <v>19</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="3">
+        <f>LEN(D23)-LEN(SUBSTITUTE(D23,"[",""))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="3">
+        <f>LEN(D24)-LEN(SUBSTITUTE(D24,"[",""))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="3">
+        <f>LEN(D25)-LEN(SUBSTITUTE(D25,"[",""))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="3">
+        <f>LEN(D26)-LEN(SUBSTITUTE(D26,"[",""))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27">
+        <v>23</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="3">
+        <f>LEN(D27)-LEN(SUBSTITUTE(D27,"[",""))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="3">
+        <f>LEN(D28)-LEN(SUBSTITUTE(D28,"[",""))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="5:5">
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="5:5">
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="5:5">
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="5:5">
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" spans="5:5">
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="5:5">
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="5:5">
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" spans="5:5">
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" spans="5:5">
+      <c r="E37" s="3"/>
+    </row>
+    <row r="38" spans="5:5">
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" spans="5:5">
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="5:5">
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="5:5">
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="5:5">
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="5:5">
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="5:5">
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="5:5">
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="5:5">
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="5:5">
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="5:5">
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="5:5">
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="5:5">
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="5:5">
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="5:5">
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="5:5">
+      <c r="E53" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/AAAGameData/DataTables/LayerTable.xlsx
+++ b/AAAGameData/DataTables/LayerTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>#</t>
   </si>
@@ -62,70 +62,105 @@
     <t>完整层（行排列）</t>
   </si>
   <si>
-    <t>[-3,3,0],[-1.5,3,0],[0,3,0],[1.5,3,0],[3,3,0],[-3,1.5,0],[-1.5,1.5,0],[0,1.5,0],[1.5,1.5,0],[3,1.5,0],[-3,0,0],[-1.5,0,0],[0,0,0],[1.5,0,0],[3,0,0],[-3,-1.5,0],[-1.5,-1.5,0],[0,-1.5,0],[1.5,-1.5,0],[3,-1.5,0],[-3,-3,0],[-1.5,-3,0],[0,-3,0],[1.5,-3,0],[3,-3,0]</t>
+    <t>[-3,4,0],[-2,4,0],[-1,4,0],[0,4,0],[1,4,0],[2,4,0],[3,4,0],[-3,3,0],[-2,3,0],[-1,3,0],[0,3,0],[1,3,0],[2,3,0],[3,3,0],[-3,2,0],[-2,2,0],[-1,2,0],[0,2,0],[1,2,0],[2,2,0],[3,2,0],[-3,1,0],[-2,1,0],[-1,1,0],[0,1,0],[1,1,0],[2,1,0],[3,1,0],[-3,0,0],[-2,0,0],[-1,0,0],[0,0,0],[1,0,0],[2,0,0],[3,0,0],[-3,-1,0],[-2,-1,0],[-1,-1,0],[0,-1,0],[1,-1,0],[2,-1,0],[3,-1,0],[-3,-2,0],[-2,-2,0],[-1,-2,0],[0,-2,0],[1,-2,0],[2,-2,0],[3,-2,0],[-3,-3,0],[-2,-3,0],[-1,-3,0],[0,-3,0],[1,-3,0],[2,-3,0],[3,-3,0]</t>
   </si>
   <si>
     <t>完整行，第1行</t>
   </si>
   <si>
-    <t>[-3,3,0],[-1.5,3,0],[0,3,0],[1.5,3,0],[3,3,0]</t>
+    <t>[-3,4,0],[-2,4,0],[-1,4,0],[0,4,0],[1,4,0],[2,4,0],[3,4,0]</t>
   </si>
   <si>
     <t>完整行，第2行</t>
   </si>
   <si>
-    <t>[-3,1.5,0],[-1.5,1.5,0],[0,1.5,0],[1.5,1.5,0],[3,1.5,0]</t>
+    <t>[-3,3,0],[-2,3,0],[-1,3,0],[0,3,0],[1,3,0],[2,3,0],[3,3,0]</t>
   </si>
   <si>
     <t>完整行，第3行</t>
   </si>
   <si>
-    <t>[-3,0,0],[-1.5,0,0],[0,0,0],[1.5,0,0],[3,0,0]</t>
+    <t>[-3,2,0],[-2,2,0],[-1,2,0],[0,2,0],[1,2,0],[2,2,0],[3,2,0]</t>
   </si>
   <si>
     <t>完整行，第4行</t>
   </si>
   <si>
-    <t>[-3,-1.5,0],[-1.5,-1.5,0],[0,-1.5,0],[1.5,-1.5,0],[3,-1.5,0]</t>
+    <t>[-3,1,0],[-2,1,0],[-1,1,0],[0,1,0],[1,1,0],[2,1,0],[3,1,0]</t>
   </si>
   <si>
     <t>完整行，第5行</t>
   </si>
   <si>
-    <t>[-3,-3,0],[-1.5,-3,0],[0,-3,0],[1.5,-3,0],[3,-3,0]</t>
+    <t>[-3,0,0],[-2,0,0],[-1,0,0],[0,0,0],[1,0,0],[2,0,0],[3,0,0]</t>
+  </si>
+  <si>
+    <t>完整行，第6行</t>
+  </si>
+  <si>
+    <t>[-3,-1,0],[-2,-1,0],[-1,-1,0],[0,-1,0],[1,-1,0],[2,-1,0],[3,-1,0]</t>
+  </si>
+  <si>
+    <t>完整行，第7行</t>
+  </si>
+  <si>
+    <t>[-3,-2,0],[-2,-2,0],[-1,-2,0],[0,-2,0],[1,-2,0],[2,-2,0],[3,-2,0]</t>
+  </si>
+  <si>
+    <t>完整行，第8行</t>
+  </si>
+  <si>
+    <t>[-3,-3,0],[-2,-3,0],[-1,-3,0],[0,-3,0],[1,-3,0],[2,-3,0],[3,-3,0]</t>
   </si>
   <si>
     <t>完整列，第1列</t>
   </si>
   <si>
-    <t>[-3,3,0],[-3,1.5,0],[-3,0,0],[-3,-1.5,0],[-3,-3,0]</t>
+    <t>[-3,4,0],[-3,3,0],[-3,2,0],[-3,1,0],[-3,0,0],[-3,-1,0],[-3,-2,0],[-3,-3,0]</t>
   </si>
   <si>
     <t>完整列，第2列</t>
   </si>
   <si>
-    <t>[-1.5,3,0],[-1.5,1.5,0],[-1.5,0,0],[-1.5,-1.5,0],[-1.5,-3,0]</t>
+    <t>[-2,4,0],[-2,3,0],[-2,2,0],[-2,1,0],[-2,0,0],[-2,-1,0],[-2,-2,0],[-2,-3,0]</t>
   </si>
   <si>
     <t>完整列，第3列</t>
   </si>
   <si>
-    <t>[0,-3,0],[0,3,0],[0,1.5,0],[0,0,0],[0,-1.5,0]</t>
+    <t>[-1,4,0],[-1,3,0],[-1,2,0],[-1,1,0],[-1,0,0],[-1,-1,0],[-1,-2,0],[-1,-3,0]</t>
   </si>
   <si>
     <t>完整列，第4列</t>
   </si>
   <si>
-    <t>[1.5,3,0],[1.5,1.5,0],[1.5,0,0],[1.5,-1.5,0],[1.5,-3,0]</t>
+    <t>[0,4,0],[0,3,0],[0,2,0],[0,1,0],[0,0,0],[0,-1,0],[0,-2,0],[0,-3,0]</t>
   </si>
   <si>
     <t>完整列，第5列</t>
   </si>
   <si>
-    <t>[3,3,0],[3,1.5,0],[3,0,0],[3,-1.5,0],[3,-3,0]</t>
-  </si>
-  <si>
-    <r>
+    <t>[1,4,0],[1,3,0],[1,2,0],[1,1,0],[1,0,0],[1,-1,0],[1,-2,0],[1,-3,0]</t>
+  </si>
+  <si>
+    <t>完整列，第6列</t>
+  </si>
+  <si>
+    <t>[2,4,0],[2,3,0],[2,2,0],[2,1,0],[2,0,0],[2,-1,0],[2,-2,0],[2,-3,0]</t>
+  </si>
+  <si>
+    <t>完整列，第7列</t>
+  </si>
+  <si>
+    <t>[3,4,0],[3,3,0],[3,2,0],[3,1,0],[3,0,0],[3,-1,0],[3,-2,0],[3,-3,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x</t>
     </r>
     <r>
@@ -138,10 +173,15 @@
     </r>
   </si>
   <si>
-    <t>[-2.25,3,0],[-0.75,3,0],[0.75,3,0],[2.25,3,0],[-2.25,1.5,0],[-0.75,1.5,0],[0.75,1.5,0],[2.25,1.5,0],[-2.25,0,0],[-0.75,0,0],[0.75,0,0],[2.25,0,0],[-2.25,-1.5,0],[-0.75,-1.5,0],[0.75,-1.5,0],[2.25,-1.5,0],[-2.25,-3,0],[-0.75,-3,0],[0.75,-3,0],[2.25,-3,0]</t>
-  </si>
-  <si>
-    <r>
+    <t>[-2.5,4,0],[-1.5,4,0],[-0.5,4,0],[0.5,4,0],[1.5,4,0],[2.5,4,0],[-2.5,3,0],[-1.5,3,0],[-0.5,3,0],[0.5,3,0],[1.5,3,0],[2.5,3,0],[-2.5,2,0],[-1.5,2,0],[-0.5,2,0],[0.5,2,0],[1.5,2,0],[2.5,2,0],[-2.5,1,0],[-1.5,1,0],[-0.5,1,0],[0.5,1,0],[1.5,1,0],[2.5,1,0],[-2.5,0,0],[-1.5,0,0],[-0.5,0,0],[0.5,0,0],[1.5,0,0],[2.5,0,0],[-2.5,-1,0],[-1.5,-1,0],[-0.5,-1,0],[0.5,-1,0],[1.5,-1,0],[2.5,-1,0],[-2.5,-2,0],[-1.5,-2,0],[-0.5,-2,0],[0.5,-2,0],[1.5,-2,0],[2.5,-2,0],[-2.5,-3,0],[-1.5,-3,0],[-0.5,-3,0],[0.5,-3,0],[1.5,-3,0],[2.5,-3,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x</t>
     </r>
     <r>
@@ -154,7 +194,7 @@
     </r>
   </si>
   <si>
-    <t>[-2.25,3,0],[-0.75,3,0],[0.75,3,0],[2.25,3,0]</t>
+    <t>[-2.5,4,0],[-1.5,4,0],[-0.5,4,0],[0.5,4,0],[1.5,4,0],[2.5,4,0]</t>
   </si>
   <si>
     <r>
@@ -166,14 +206,35 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>偏移半格，第2行</t>
-    </r>
-  </si>
-  <si>
-    <t>[-2.25,1.5,0],[-0.75,1.5,0],[0.75,1.5,0],[2.25,1.5,0]</t>
-  </si>
-  <si>
-    <r>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.5,3,0],[-1.5,3,0],[-0.5,3,0],[0.5,3,0],[1.5,3,0],[2.5,3,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x</t>
     </r>
     <r>
@@ -186,7 +247,7 @@
     </r>
   </si>
   <si>
-    <t>[-2.25,0,0],[-0.75,0,0],[0.75,0,0],[2.25,0,0]</t>
+    <t>[-2.5,2,0],[-1.5,2,0],[-0.5,2,0],[0.5,2,0],[1.5,2,0],[2.5,2,0]</t>
   </si>
   <si>
     <r>
@@ -198,14 +259,35 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>偏移半格，第4行</t>
-    </r>
-  </si>
-  <si>
-    <t>[-2.25,-1.5,0],[-0.75,-1.5,0],[0.75,-1.5,0],[2.25,-1.5,0]</t>
-  </si>
-  <si>
-    <r>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.5,1,0],[-1.5,1,0],[-0.5,1,0],[0.5,1,0],[1.5,1,0],[2.5,1,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x</t>
     </r>
     <r>
@@ -218,10 +300,100 @@
     </r>
   </si>
   <si>
-    <t>[-2.25,-3,0],[-0.75,-3,0],[0.75,-3,0],[2.25,-3,0]</t>
-  </si>
-  <si>
-    <r>
+    <t>[-2.5,0,0],[-1.5,0,0],[-0.5,0,0],[0.5,0,0],[1.5,0,0],[2.5,0,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.5,-1,0],[-1.5,-1,0],[-0.5,-1,0],[0.5,-1,0],[1.5,-1,0],[2.5,-1,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第7行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.5,-2,0],[-1.5,-2,0],[-0.5,-2,0],[0.5,-2,0],[1.5,-2,0],[2.5,-2,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.5,-3,0],[-1.5,-3,0],[-0.5,-3,0],[0.5,-3,0],[1.5,-3,0],[2.5,-3,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x/y</t>
     </r>
     <r>
@@ -234,7 +406,7 @@
     </r>
   </si>
   <si>
-    <t>[-2.25,2.25,0],[-0.75,2.25,0],[0.75,2.25,0],[2.25,2.25,0],[-2.25,0.75,0],[-0.75,0.75,0],[0.75,0.75,0],[2.25,0.75,0],[-2.25,-0.75,0],[-0.75,-0.75,0],[0.75,-0.75,0],[2.25,-0.75,0],[-2.25,-2.25,0],[-0.75,-2.25,0],[0.75,-2.25,0],[2.25,-2.25,0]</t>
+    <t>[-2.5,3.5,0],[-1.5,3.5,0],[-0.5,3.5,0],[0.5,3.5,0],[1.5,3.5,0],[2.5,3.5,0],[-2.5,2.5,0],[-1.5,2.5,0],[-0.5,2.5,0],[0.5,2.5,0],[1.5,2.5,0],[2.5,2.5,0],[-2.5,1.5,0],[-1.5,1.5,0],[-0.5,1.5,0],[0.5,1.5,0],[1.5,1.5,0],[2.5,1.5,0],[-2.5,0.5,0],[-1.5,0.5,0],[-0.5,0.5,0],[0.5,0.5,0],[1.5,0.5,0],[2.5,0.5,0],[-2.5,-0.5,0],[-1.5,-0.5,0],[-0.5,-0.5,0],[0.5,-0.5,0],[1.5,-0.5,0],[2.5,-0.5,0],[-2.5,-1.5,0],[-1.5,-1.5,0],[-0.5,-1.5,0],[0.5,-1.5,0],[1.5,-1.5,0],[2.5,-1.5,0],[-2.5,-2.5,0],[-1.5,-2.5,0],[-0.5,-2.5,0],[0.5,-2.5,0],[1.5,-2.5,0],[2.5,-2.5,0]</t>
   </si>
   <si>
     <r>
@@ -266,7 +438,7 @@
     </r>
   </si>
   <si>
-    <t>[-2.25,2.25,0],[-0.75,2.25,0],[0.75,2.25,0],[2.25,2.25,0]</t>
+    <t>[-2.5,3.5,0],[-1.5,3.5,0],[-0.5,3.5,0],[0.5,3.5,0],[1.5,3.5,0],[2.5,3.5,0]</t>
   </si>
   <si>
     <r>
@@ -298,7 +470,7 @@
     </r>
   </si>
   <si>
-    <t>[-2.25,0.75,0],[-0.75,0.75,0],[0.75,0.75,0],[2.25,0.75,0]</t>
+    <t>[-2.5,2.5,0],[-1.5,2.5,0],[-0.5,2.5,0],[0.5,2.5,0],[1.5,2.5,0],[2.5,2.5,0]</t>
   </si>
   <si>
     <r>
@@ -330,7 +502,7 @@
     </r>
   </si>
   <si>
-    <t>[-2.25,-0.75,0],[-0.75,-0.75,0],[0.75,-0.75,0],[2.25,-0.75,0]</t>
+    <t>[-2.5,1.5,0],[-1.5,1.5,0],[-0.5,1.5,0],[0.5,1.5,0],[1.5,1.5,0],[2.5,1.5,0]</t>
   </si>
   <si>
     <r>
@@ -362,19 +534,103 @@
     </r>
   </si>
   <si>
-    <t>[-2.25,-2.25,0],[-0.75,-2.25,0],[0.75,-2.25,0],[2.25,-2.25,0]</t>
-  </si>
-  <si>
-    <t>居中十字</t>
-  </si>
-  <si>
-    <t>[-3,0,0],[-1.5,0,0],[0,0,0],[1.5,0,0],[3,0,0],[0,-3,0],[0,3,0],[0,1.5,0],[0,-1.5,0]</t>
-  </si>
-  <si>
-    <t>双对角线</t>
-  </si>
-  <si>
-    <t>[-3,3,0],[3,3,0],[-1.5,1.5,0],[1.5,1.5,0],[0,0,0],[-1.5,-1.5,0],[1.5,-1.5,0],[-3,-3,0],[3,-3,0]</t>
+    <t>[-2.5,0.5,0],[-1.5,0.5,0],[-0.5,0.5,0],[0.5,0.5,0],[1.5,0.5,0],[2.5,0.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x/y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.5,-0.5,0],[-1.5,-0.5,0],[-0.5,-0.5,0],[0.5,-0.5,0],[1.5,-0.5,0],[2.5,-0.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x/y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.5,-1.5,0],[-1.5,-1.5,0],[-0.5,-1.5,0],[0.5,-1.5,0],[1.5,-1.5,0],[2.5,-1.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <t>x/y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.5,-2.5,0],[-1.5,-2.5,0],[-0.5,-2.5,0],[0.5,-2.5,0],[1.5,-2.5,0],[2.5,-2.5,0]</t>
   </si>
 </sst>
 </file>
@@ -1537,11 +1793,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="18.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="189" customWidth="1"/>
+    <col min="4" max="4" width="237.727272727273" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1607,12 +1863,12 @@
       </c>
       <c r="E5" s="3">
         <f>LEN(D5)-LEN(SUBSTITUTE(D5,"[",""))</f>
-        <v>25</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="2:5">
       <c r="B6">
-        <v>2</v>
+        <v>1001</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
@@ -1622,12 +1878,12 @@
       </c>
       <c r="E6" s="3">
         <f>LEN(D6)-LEN(SUBSTITUTE(D6,"[",""))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="2:5">
       <c r="B7">
-        <v>3</v>
+        <v>1002</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>14</v>
@@ -1636,13 +1892,13 @@
         <v>15</v>
       </c>
       <c r="E7" s="3">
-        <f>LEN(D7)-LEN(SUBSTITUTE(D7,"[",""))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
+        <f t="shared" ref="E7:E13" si="0">LEN(D7)-LEN(SUBSTITUTE(D7,"[",""))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="2:5">
       <c r="B8">
-        <v>4</v>
+        <v>1003</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>16</v>
@@ -1651,13 +1907,13 @@
         <v>17</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" ref="E8:E15" si="0">LEN(D8)-LEN(SUBSTITUTE(D8,"[",""))</f>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9">
-        <v>5</v>
+        <v>1004</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>18</v>
@@ -1667,12 +1923,12 @@
       </c>
       <c r="E9" s="3">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10">
-        <v>6</v>
+        <v>1005</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>20</v>
@@ -1682,12 +1938,12 @@
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="B11">
-        <v>7</v>
+        <v>1006</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>22</v>
@@ -1697,12 +1953,12 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="2:5">
       <c r="B12">
-        <v>8</v>
+        <v>1007</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>24</v>
@@ -1712,12 +1968,12 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="2:5">
       <c r="B13">
-        <v>9</v>
+        <v>1008</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>26</v>
@@ -1727,12 +1983,12 @@
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14">
-        <v>10</v>
+        <v>1009</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>28</v>
@@ -1741,13 +1997,13 @@
         <v>29</v>
       </c>
       <c r="E14" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ref="E14:E20" si="1">LEN(D14)-LEN(SUBSTITUTE(D14,"[",""))</f>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="B15">
-        <v>11</v>
+        <v>1010</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>30</v>
@@ -1756,30 +2012,30 @@
         <v>31</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="B16">
-        <v>12</v>
-      </c>
-      <c r="C16" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D16" t="s">
         <v>33</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" ref="E16:E24" si="1">LEN(D16)-LEN(SUBSTITUTE(D16,"[",""))</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17">
-        <v>13</v>
-      </c>
-      <c r="C17" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D17" t="s">
@@ -1787,14 +2043,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18">
-        <v>14</v>
-      </c>
-      <c r="C18" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D18" t="s">
@@ -1802,14 +2058,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="2:5">
       <c r="B19">
-        <v>15</v>
-      </c>
-      <c r="C19" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D19" t="s">
@@ -1817,14 +2073,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="2:5">
       <c r="B20">
-        <v>16</v>
-      </c>
-      <c r="C20" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D20" t="s">
@@ -1832,12 +2088,12 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>42</v>
@@ -1846,13 +2102,13 @@
         <v>43</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
+        <f>LEN(D21)-LEN(SUBSTITUTE(D21,"[",""))</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="2:5">
       <c r="B22">
-        <v>18</v>
+        <v>2001</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>44</v>
@@ -1862,12 +2118,12 @@
       </c>
       <c r="E22" s="3">
         <f>LEN(D22)-LEN(SUBSTITUTE(D22,"[",""))</f>
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23">
-        <v>19</v>
+        <v>2002</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>46</v>
@@ -1876,13 +2132,13 @@
         <v>47</v>
       </c>
       <c r="E23" s="3">
-        <f>LEN(D23)-LEN(SUBSTITUTE(D23,"[",""))</f>
-        <v>4</v>
+        <f t="shared" ref="E23:E29" si="2">LEN(D23)-LEN(SUBSTITUTE(D23,"[",""))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24">
-        <v>20</v>
+        <v>2003</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>48</v>
@@ -1891,13 +2147,13 @@
         <v>49</v>
       </c>
       <c r="E24" s="3">
-        <f>LEN(D24)-LEN(SUBSTITUTE(D24,"[",""))</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25">
-        <v>21</v>
+        <v>2004</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>50</v>
@@ -1906,13 +2162,13 @@
         <v>51</v>
       </c>
       <c r="E25" s="3">
-        <f>LEN(D25)-LEN(SUBSTITUTE(D25,"[",""))</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="B26">
-        <v>22</v>
+        <v>2005</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>52</v>
@@ -1921,71 +2177,183 @@
         <v>53</v>
       </c>
       <c r="E26" s="3">
-        <f>LEN(D26)-LEN(SUBSTITUTE(D26,"[",""))</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27">
-        <v>23</v>
-      </c>
-      <c r="C27" s="3" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D27" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="3">
-        <f>LEN(D27)-LEN(SUBSTITUTE(D27,"[",""))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="2:5">
       <c r="B28">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D28" t="s">
         <v>57</v>
       </c>
       <c r="E28" s="3">
-        <f>LEN(D28)-LEN(SUBSTITUTE(D28,"[",""))</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="5:5">
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="5:5">
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" spans="5:5">
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="5:5">
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="5:5">
-      <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="5:5">
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="5:5">
-      <c r="E35" s="3"/>
-    </row>
-    <row r="36" spans="5:5">
-      <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="5:5">
-      <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="5:5">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="2:5">
+      <c r="B29">
+        <v>2008</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="3">
+        <f>LEN(D30)-LEN(SUBSTITUTE(D30,"[",""))</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="2:5">
+      <c r="B31">
+        <v>3001</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="3">
+        <f>LEN(D31)-LEN(SUBSTITUTE(D31,"[",""))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32">
+        <v>3002</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" s="3">
+        <f>LEN(D32)-LEN(SUBSTITUTE(D32,"[",""))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33">
+        <v>3003</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="3">
+        <f>LEN(D33)-LEN(SUBSTITUTE(D33,"[",""))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34">
+        <v>3004</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="3">
+        <f>LEN(D34)-LEN(SUBSTITUTE(D34,"[",""))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35">
+        <v>3005</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="3">
+        <f>LEN(D35)-LEN(SUBSTITUTE(D35,"[",""))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36">
+        <v>3006</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="3">
+        <f>LEN(D36)-LEN(SUBSTITUTE(D36,"[",""))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37">
+        <v>3007</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="3">
+        <f>LEN(D37)-LEN(SUBSTITUTE(D37,"[",""))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5">
+      <c r="C38" s="3"/>
+      <c r="D38"/>
       <c r="E38" s="3"/>
     </row>
-    <row r="39" spans="5:5">
+    <row r="39" spans="3:5">
+      <c r="C39" s="3"/>
+      <c r="D39"/>
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="5:5">
@@ -2029,6 +2397,39 @@
     </row>
     <row r="53" spans="5:5">
       <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="5:5">
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="5:5">
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" spans="5:5">
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="5:5">
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="5:5">
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="5:5">
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" spans="5:5">
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="5:5">
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" spans="5:5">
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" spans="5:5">
+      <c r="E63" s="3"/>
+    </row>
+    <row r="64" spans="5:5">
+      <c r="E64" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/AAAGameData/DataTables/LayerTable.xlsx
+++ b/AAAGameData/DataTables/LayerTable.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GameCode\Cat V4.0\AAAGameData\DataTables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5835CB87-5145-495B-B752-D4ADA946EB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="95">
   <si>
     <t>#</t>
   </si>
@@ -148,11 +155,29 @@
     <t>[3,4,0],[3,3,0],[3,2,0],[3,1,0],[3,0,0],[3,-1,0],[3,-2,0],[3,-3,0]</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>详见表格</t>
+  </si>
+  <si>
+    <t>[-2,2,0],[-1,2,0],[0,2,0],[1,2,0],[2,2,0]</t>
+  </si>
+  <si>
+    <t>[-1,0,0],[0,0,0],[1,0,0]</t>
+  </si>
+  <si>
+    <t>[0,-2,0]</t>
+  </si>
+  <si>
+    <t>[-3,4,0],[-2,4,0],[-1,4,0],[0,4,0],[1,4,0],[2,4,0],[3,4,0],[-2,3,0],[-1,3,0],[0,3,0],[1,3,0],[2,3,0],[-1,2,0],[0,2,0],[1,2,0],[0,1,0],[-3,-1,0],[-2,-1,0],[-1,-1,0],[0,-1,0],[1,-1,0],[2,-1,0],[3,-1,0],[-3,-3,0],[3,-3,0]</t>
+  </si>
+  <si>
+    <t>[-3,-3,0],[3,-3,0],[-3,-2.95,0],[3,-2.95,0],[-3,-2.9,0],[3,-2.9,0],[-3,-2.85,0],[3,-2.85,0],[-3,-2.8,0],[3,-2.8,0],[-3,-2.75,0],[3,-2.75,0],[-3,-2.7,0],[3,-2.7,0],[-3,-2.65,0],[3,-2.65,0],[-3,-2.6,0],[3,-2.6,0],[-3,-2.55,0],[3,-2.55,0],[-3,-2.5,0],[3,-2.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>x</t>
     </r>
@@ -166,11 +191,14 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>[-2.5,4,0],[-1.5,4,0],[-0.5,4,0],[0.5,4,0],[1.5,4,0],[2.5,4,0],[-2.5,3,0],[-1.5,3,0],[-0.5,3,0],[0.5,3,0],[1.5,3,0],[2.5,3,0],[-2.5,2,0],[-1.5,2,0],[-0.5,2,0],[0.5,2,0],[1.5,2,0],[2.5,2,0],[-2.5,1,0],[-1.5,1,0],[-0.5,1,0],[0.5,1,0],[1.5,1,0],[2.5,1,0],[-2.5,0,0],[-1.5,0,0],[-0.5,0,0],[0.5,0,0],[1.5,0,0],[2.5,0,0],[-2.5,-1,0],[-1.5,-1,0],[-0.5,-1,0],[0.5,-1,0],[1.5,-1,0],[2.5,-1,0],[-2.5,-2,0],[-1.5,-2,0],[-0.5,-2,0],[0.5,-2,0],[1.5,-2,0],[2.5,-2,0],[-2.5,-3,0],[-1.5,-3,0],[-0.5,-3,0],[0.5,-3,0],[1.5,-3,0],[2.5,-3,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>x</t>
     </r>
@@ -184,7 +212,15 @@
     </r>
   </si>
   <si>
-    <r>
+    <t>[-2.5,4,0],[-1.5,4,0],[-0.5,4,0],[0.5,4,0],[1.5,4,0],[2.5,4,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x</t>
     </r>
     <r>
@@ -199,7 +235,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>2</t>
     </r>
@@ -220,7 +256,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>x</t>
     </r>
@@ -238,6 +274,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x</t>
     </r>
     <r>
@@ -252,7 +293,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>4</t>
     </r>
@@ -273,7 +314,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>x</t>
     </r>
@@ -291,6 +332,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x</t>
     </r>
     <r>
@@ -305,7 +351,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>6</t>
     </r>
@@ -319,11 +365,14 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>[-2.5,-1,0],[-1.5,-1,0],[-0.5,-1,0],[0.5,-1,0],[1.5,-1,0],[2.5,-1,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>x</t>
     </r>
@@ -337,7 +386,15 @@
     </r>
   </si>
   <si>
-    <r>
+    <t>[-2.5,-2,0],[-1.5,-2,0],[-0.5,-2,0],[0.5,-2,0],[1.5,-2,0],[2.5,-2,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x</t>
     </r>
     <r>
@@ -352,7 +409,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>8</t>
     </r>
@@ -370,6 +427,125 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第2行（4格）</t>
+    </r>
+  </si>
+  <si>
+    <t>[-1.5,3,0],[-0.5,3,0],[0.5,3,0],[1.5,3,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第4行（4格）</t>
+    </r>
+  </si>
+  <si>
+    <t>[-1.5,1,0],[-0.5,1,0],[0.5,1,0],[1.5,1,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第6行（2格）</t>
+    </r>
+  </si>
+  <si>
+    <t>[-0.5,-1,0],[0.5,-1,0]</t>
+  </si>
+  <si>
+    <t>[-2.5,4,0],[-1.5,4,0],[-0.5,4,0],[0.5,4,0],[1.5,4,0],[2.5,4,0],[-1.5,3,0],[-0.5,3,0],[0.5,3,0],[1.5,3,0],[-0.5,2,0],[0.5,2,0],[-2.5,-1,0],[-1.5,-1,0],[-0.5,-1,0],[0.5,-1,0],[1.5,-1,0],[2.5,-1,0]</t>
+  </si>
+  <si>
+    <t>y偏移半格，完成层</t>
+  </si>
+  <si>
+    <t>[-3,3.5,0],[-2,3.5,0],[-1,3.5,0],[0,3.5,0],[1,3.5,0],[2,3.5,0],[3,3.5,0],[-3,2.5,0],[-2,2.5,0],[-1,2.5,0],[0,2.5,0],[1,2.5,0],[2,2.5,0],[3,2.5,0],[-3,1.5,0],[-2,1.5,0],[-1,1.5,0],[0,1.5,0],[1,1.5,0],[2,1.5,0],[3,1.5,0],[-3,0.5,0],[-2,0.5,0],[-1,0.5,0],[0,0.5,0],[1,0.5,0],[2,0.5,0],[3,0.5,0],[-3,-0.5,0],[-2,-0.5,0],[-1,-0.5,0],[0,-0.5,0],[1,-0.5,0],[2,-0.5,0],[3,-0.5,0],[-3,-1.5,0],[-2,-1.5,0],[-1,-1.5,0],[0,-1.5,0],[1,-1.5,0],[2,-1.5,0],[3,-1.5,0],[-3,-2.5,0],[-2,-2.5,0],[-1,-2.5,0],[0,-2.5,0],[1,-2.5,0],[2,-2.5,0],[3,-2.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第1行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-3,3.5,0],[-2,3.5,0],[-1,3.5,0],[0,3.5,0],[1,3.5,0],[2,3.5,0],[3,3.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏移半格，第2行</t>
+    </r>
+  </si>
+  <si>
+    <t>[-3,2.5,0],[-2,2.5,0],[-1,2.5,0],[0,2.5,0],[1,2.5,0],[2,2.5,0],[3,2.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x/y</t>
     </r>
     <r>
@@ -378,13 +554,34 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
+      <t>偏移半格，完整层</t>
+    </r>
+  </si>
+  <si>
+    <t>[-2.5,3.5,0],[-1.5,3.5,0],[-0.5,3.5,0],[0.5,3.5,0],[1.5,3.5,0],[2.5,3.5,0],[-2.5,2.5,0],[-1.5,2.5,0],[-0.5,2.5,0],[0.5,2.5,0],[1.5,2.5,0],[2.5,2.5,0],[-2.5,1.5,0],[-1.5,1.5,0],[-0.5,1.5,0],[0.5,1.5,0],[1.5,1.5,0],[2.5,1.5,0],[-2.5,0.5,0],[-1.5,0.5,0],[-0.5,0.5,0],[0.5,0.5,0],[1.5,0.5,0],[2.5,0.5,0],[-2.5,-0.5,0],[-1.5,-0.5,0],[-0.5,-0.5,0],[0.5,-0.5,0],[1.5,-0.5,0],[2.5,-0.5,0],[-2.5,-1.5,0],[-1.5,-1.5,0],[-0.5,-1.5,0],[0.5,-1.5,0],[1.5,-1.5,0],[2.5,-1.5,0],[-2.5,-2.5,0],[-1.5,-2.5,0],[-0.5,-2.5,0],[0.5,-2.5,0],[1.5,-2.5,0],[2.5,-2.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x/y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>偏移半格，第</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>1</t>
     </r>
@@ -398,7 +595,15 @@
     </r>
   </si>
   <si>
-    <r>
+    <t>[-2.5,3.5,0],[-1.5,3.5,0],[-0.5,3.5,0],[0.5,3.5,0],[1.5,3.5,0],[2.5,3.5,0]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x/y</t>
     </r>
     <r>
@@ -413,7 +618,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>2</t>
     </r>
@@ -431,6 +636,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x/y</t>
     </r>
     <r>
@@ -445,7 +655,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>3</t>
     </r>
@@ -463,6 +673,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x/y</t>
     </r>
     <r>
@@ -477,7 +692,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>4</t>
     </r>
@@ -495,6 +710,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x/y</t>
     </r>
     <r>
@@ -509,7 +729,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>5</t>
     </r>
@@ -527,6 +747,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x/y</t>
     </r>
     <r>
@@ -541,7 +766,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>6</t>
     </r>
@@ -559,6 +784,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>x/y</t>
     </r>
     <r>
@@ -573,7 +803,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>7</t>
     </r>
@@ -588,180 +818,19 @@
   </si>
   <si>
     <t>[-2.5,-2.5,0],[-1.5,-2.5,0],[-0.5,-2.5,0],[0.5,-2.5,0],[1.5,-2.5,0],[2.5,-2.5,0]</t>
-  </si>
-  <si>
-    <t>[-2.5,4,0],[-1.5,4,0],[-0.5,4,0],[0.5,4,0],[1.5,4,0],[2.5,4,0],[-2.5,3,0],[-1.5,3,0],[-0.5,3,0],[0.5,3,0],[1.5,3,0],[2.5,3,0],[-2.5,2,0],[-1.5,2,0],[-0.5,2,0],[0.5,2,0],[1.5,2,0],[2.5,2,0],[-2.5,1,0],[-1.5,1,0],[-0.5,1,0],[0.5,1,0],[1.5,1,0],[2.5,1,0],[-2.5,0,0],[-1.5,0,0],[-0.5,0,0],[0.5,0,0],[1.5,0,0],[2.5,0,0],[-2.5,-1,0],[-1.5,-1,0],[-0.5,-1,0],[0.5,-1,0],[1.5,-1,0],[2.5,-1,0],[-2.5,-2,0],[-1.5,-2,0],[-0.5,-2,0],[0.5,-2,0],[1.5,-2,0],[2.5,-2,0],[-2.5,-3,0],[-1.5,-3,0],[-0.5,-3,0],[0.5,-3,0],[1.5,-3,0],[2.5,-3,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-2.5,4,0],[-1.5,4,0],[-0.5,4,0],[0.5,4,0],[1.5,4,0],[2.5,4,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-2.5,3.5,0],[-1.5,3.5,0],[-0.5,3.5,0],[0.5,3.5,0],[1.5,3.5,0],[2.5,3.5,0],[-2.5,2.5,0],[-1.5,2.5,0],[-0.5,2.5,0],[0.5,2.5,0],[1.5,2.5,0],[2.5,2.5,0],[-2.5,1.5,0],[-1.5,1.5,0],[-0.5,1.5,0],[0.5,1.5,0],[1.5,1.5,0],[2.5,1.5,0],[-2.5,0.5,0],[-1.5,0.5,0],[-0.5,0.5,0],[0.5,0.5,0],[1.5,0.5,0],[2.5,0.5,0],[-2.5,-0.5,0],[-1.5,-0.5,0],[-0.5,-0.5,0],[0.5,-0.5,0],[1.5,-0.5,0],[2.5,-0.5,0],[-2.5,-1.5,0],[-1.5,-1.5,0],[-0.5,-1.5,0],[0.5,-1.5,0],[1.5,-1.5,0],[2.5,-1.5,0],[-2.5,-2.5,0],[-1.5,-2.5,0],[-0.5,-2.5,0],[0.5,-2.5,0],[1.5,-2.5,0],[2.5,-2.5,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>x/y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>偏移半格，完整层</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-2.5,3.5,0],[-1.5,3.5,0],[-0.5,3.5,0],[0.5,3.5,0],[1.5,3.5,0],[2.5,3.5,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>y偏移半格，完成层</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-3,3.5,0],[-2,3.5,0],[-1,3.5,0],[0,3.5,0],[1,3.5,0],[2,3.5,0],[3,3.5,0],[-3,2.5,0],[-2,2.5,0],[-1,2.5,0],[0,2.5,0],[1,2.5,0],[2,2.5,0],[3,2.5,0],[-3,1.5,0],[-2,1.5,0],[-1,1.5,0],[0,1.5,0],[1,1.5,0],[2,1.5,0],[3,1.5,0],[-3,0.5,0],[-2,0.5,0],[-1,0.5,0],[0,0.5,0],[1,0.5,0],[2,0.5,0],[3,0.5,0],[-3,-0.5,0],[-2,-0.5,0],[-1,-0.5,0],[0,-0.5,0],[1,-0.5,0],[2,-0.5,0],[3,-0.5,0],[-3,-1.5,0],[-2,-1.5,0],[-1,-1.5,0],[0,-1.5,0],[1,-1.5,0],[2,-1.5,0],[3,-1.5,0],[-3,-2.5,0],[-2,-2.5,0],[-1,-2.5,0],[0,-2.5,0],[1,-2.5,0],[2,-2.5,0],[3,-2.5,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>偏移半格，第1行</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-1.5,3,0],[-0.5,3,0],[0.5,3,0],[1.5,3,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>x</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>偏移半格，第2行（4格）</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>偏移半格，第2行</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>详见表格</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-2,2,0],[-1,2,0],[0,2,0],[1,2,0],[2,2,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>x</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>偏移半格，第4行（4格）</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-1.5,1,0],[-0.5,1,0],[0.5,1,0],[1.5,1,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-1,0,0],[0,0,0],[1,0,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>x</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>偏移半格，第6行（2格）</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-0.5,-1,0],[0.5,-1,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[0,-2,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-2.5,-2,0],[-1.5,-2,0],[-0.5,-2,0],[0.5,-2,0],[1.5,-2,0],[2.5,-2,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-2.5,-1,0],[-1.5,-1,0],[-0.5,-1,0],[0.5,-1,0],[1.5,-1,0],[2.5,-1,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-3,3.5,0],[-2,3.5,0],[-1,3.5,0],[0,3.5,0],[1,3.5,0],[2,3.5,0],[3,3.5,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[-3,2.5,0],[-2,2.5,0],[-1,2.5,0],[0,2.5,0],[1,2.5,0],[2,2.5,0],[3,2.5,0]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -781,36 +850,354 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -818,171 +1205,343 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -993,7 +1552,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1021,40 +1580,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1312,21 +1985,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="39.5703125" customWidth="1"/>
-    <col min="4" max="4" width="237.7109375" customWidth="1"/>
+    <col min="3" max="3" width="39.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="237.709090909091" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1376,7 +2049,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" customFormat="1" spans="2:5">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1387,11 +2060,11 @@
         <v>11</v>
       </c>
       <c r="E5" s="3">
-        <f>LEN(D5)-LEN(SUBSTITUTE(D5,"[",""))</f>
+        <f t="shared" ref="E5:E37" si="0">LEN(D5)-LEN(SUBSTITUTE(D5,"[",""))</f>
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" customFormat="1" spans="2:5">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1402,11 +2075,11 @@
         <v>13</v>
       </c>
       <c r="E6" s="3">
-        <f>LEN(D6)-LEN(SUBSTITUTE(D6,"[",""))</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" customFormat="1" spans="2:5">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1417,11 +2090,11 @@
         <v>15</v>
       </c>
       <c r="E7" s="3">
-        <f t="shared" ref="E7:E13" si="0">LEN(D7)-LEN(SUBSTITUTE(D7,"[",""))</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" customFormat="1" spans="2:5">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1436,7 +2109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" customFormat="1" spans="2:5">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1451,7 +2124,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" customFormat="1" spans="2:5">
       <c r="B10">
         <v>1005</v>
       </c>
@@ -1466,7 +2139,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" customFormat="1" spans="2:5">
       <c r="B11">
         <v>1006</v>
       </c>
@@ -1481,7 +2154,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" customFormat="1" spans="2:5">
       <c r="B12">
         <v>1007</v>
       </c>
@@ -1496,7 +2169,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" customFormat="1" spans="2:5">
       <c r="B13">
         <v>1008</v>
       </c>
@@ -1511,7 +2184,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" customFormat="1" spans="2:5">
       <c r="B14">
         <v>1009</v>
       </c>
@@ -1522,11 +2195,11 @@
         <v>29</v>
       </c>
       <c r="E14" s="3">
-        <f t="shared" ref="E14:E22" si="1">LEN(D14)-LEN(SUBSTITUTE(D14,"[",""))</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" customFormat="1" spans="2:5">
       <c r="B15">
         <v>1010</v>
       </c>
@@ -1537,11 +2210,11 @@
         <v>31</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" customFormat="1" spans="2:5">
       <c r="B16">
         <v>1011</v>
       </c>
@@ -1552,11 +2225,11 @@
         <v>33</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" customFormat="1" spans="2:5">
       <c r="B17">
         <v>1012</v>
       </c>
@@ -1567,11 +2240,11 @@
         <v>35</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" customFormat="1" spans="2:5">
       <c r="B18">
         <v>1013</v>
       </c>
@@ -1582,11 +2255,11 @@
         <v>37</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" customFormat="1" spans="2:5">
       <c r="B19">
         <v>1014</v>
       </c>
@@ -1597,11 +2270,11 @@
         <v>39</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" customFormat="1" spans="2:5">
       <c r="B20">
         <v>1015</v>
       </c>
@@ -1612,410 +2285,444 @@
         <v>41</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" customFormat="1" spans="2:5">
       <c r="B21">
         <v>1018</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>81</v>
+      <c r="C21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" customFormat="1" spans="2:5">
       <c r="B22">
         <v>1028</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>84</v>
+      <c r="C22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" customFormat="1" spans="2:5">
       <c r="B23">
         <v>1038</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>87</v>
+      <c r="C23" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" ref="E23" si="2">LEN(D23)-LEN(SUBSTITUTE(D23,"[",""))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" customFormat="1" spans="2:5">
       <c r="B24">
+        <v>1040</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="2:5">
+      <c r="B25">
+        <v>1042</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="2:5">
+      <c r="B26">
         <v>2</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="2:5">
+      <c r="B27">
+        <v>2001</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="2:5">
+      <c r="B28">
+        <v>2002</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="2:5">
+      <c r="B29">
+        <v>2003</v>
+      </c>
+      <c r="C29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="2:5">
+      <c r="B30">
+        <v>2004</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="2:5">
+      <c r="B31">
+        <v>2005</v>
+      </c>
+      <c r="C31" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="2:5">
+      <c r="B32">
+        <v>2006</v>
+      </c>
+      <c r="C32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="2:5">
+      <c r="B33">
+        <v>2007</v>
+      </c>
+      <c r="C33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="2:5">
+      <c r="B34">
+        <v>2008</v>
+      </c>
+      <c r="C34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="2:5">
+      <c r="B35">
+        <v>2010</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="2:5">
+      <c r="B36">
+        <v>2012</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="2:5">
+      <c r="B37">
+        <v>2022</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="2:5">
+      <c r="B38">
+        <v>2025</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="3">
-        <f>LEN(D24)-LEN(SUBSTITUTE(D24,"[",""))</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25">
-        <v>2001</v>
-      </c>
-      <c r="C25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="3">
-        <f>LEN(D25)-LEN(SUBSTITUTE(D25,"[",""))</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26">
-        <v>2002</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="3">
-        <f t="shared" ref="E26:E33" si="3">LEN(D26)-LEN(SUBSTITUTE(D26,"[",""))</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27">
-        <v>2003</v>
-      </c>
-      <c r="C27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="3">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28">
-        <v>2004</v>
-      </c>
-      <c r="C28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" s="3">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29">
-        <v>2005</v>
-      </c>
-      <c r="C29" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" t="s">
-        <v>51</v>
-      </c>
-      <c r="E29" s="3">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30">
-        <v>2006</v>
-      </c>
-      <c r="C30" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E30" s="3">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
-      <c r="B31">
-        <v>2007</v>
-      </c>
-      <c r="C31" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="3">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
-      <c r="B32">
-        <v>2008</v>
-      </c>
-      <c r="C32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="3">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33">
-        <v>2010</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="3">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="B34">
-        <v>2012</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E34" s="3">
-        <f t="shared" ref="E34" si="4">LEN(D34)-LEN(SUBSTITUTE(D34,"[",""))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5">
-      <c r="B35">
-        <v>2022</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E35" s="3">
-        <f t="shared" ref="E35" si="5">LEN(D35)-LEN(SUBSTITUTE(D35,"[",""))</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36">
-        <v>3</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E36" s="3">
-        <f>LEN(D36)-LEN(SUBSTITUTE(D36,"[",""))</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5">
-      <c r="B37">
-        <v>3001</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E37" s="3">
-        <f>LEN(D37)-LEN(SUBSTITUTE(D37,"[",""))</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5">
-      <c r="B38">
-        <v>3002</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>91</v>
+      <c r="D38" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="E38" s="3">
         <f>LEN(D38)-LEN(SUBSTITUTE(D38,"[",""))</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="2:5">
+      <c r="B39">
+        <v>3</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" ref="E39:E49" si="1">LEN(D39)-LEN(SUBSTITUTE(D39,"[",""))</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="2:5">
+      <c r="B40">
+        <v>3001</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" s="3">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="2:5">
-      <c r="B39">
+    <row r="41" customFormat="1" spans="2:5">
+      <c r="B41">
+        <v>3002</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" s="3">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="2:5">
+      <c r="B42">
         <v>4</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E39" s="3">
-        <f t="shared" ref="E39:E46" si="6">LEN(D39)-LEN(SUBSTITUTE(D39,"[",""))</f>
+      <c r="C42" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="2:5">
-      <c r="B40">
+    <row r="43" customFormat="1" spans="2:5">
+      <c r="B43">
         <v>4001</v>
       </c>
-      <c r="C40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" s="3">
-        <f t="shared" si="6"/>
+      <c r="C43" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="2:5">
-      <c r="B41">
+    <row r="44" customFormat="1" spans="2:5">
+      <c r="B44">
         <v>4002</v>
       </c>
-      <c r="C41" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="3">
-        <f t="shared" si="6"/>
+      <c r="C44" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="3">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="2:5">
-      <c r="B42">
+    <row r="45" customFormat="1" spans="2:5">
+      <c r="B45">
         <v>4003</v>
       </c>
-      <c r="C42" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="3">
-        <f t="shared" si="6"/>
+      <c r="C45" t="s">
+        <v>85</v>
+      </c>
+      <c r="D45" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
-      <c r="B43">
+    <row r="46" customFormat="1" spans="2:5">
+      <c r="B46">
         <v>4004</v>
       </c>
-      <c r="C43" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="3">
-        <f t="shared" si="6"/>
+      <c r="C46" t="s">
+        <v>87</v>
+      </c>
+      <c r="D46" t="s">
+        <v>88</v>
+      </c>
+      <c r="E46" s="3">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="2:5">
-      <c r="B44">
+    <row r="47" customFormat="1" spans="2:5">
+      <c r="B47">
         <v>4005</v>
       </c>
-      <c r="C44" t="s">
-        <v>63</v>
-      </c>
-      <c r="D44" t="s">
-        <v>64</v>
-      </c>
-      <c r="E44" s="3">
-        <f t="shared" si="6"/>
+      <c r="C47" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="3">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="2:5">
-      <c r="B45">
+    <row r="48" customFormat="1" spans="2:5">
+      <c r="B48">
         <v>4006</v>
       </c>
-      <c r="C45" t="s">
-        <v>65</v>
-      </c>
-      <c r="D45" t="s">
-        <v>66</v>
-      </c>
-      <c r="E45" s="3">
-        <f t="shared" si="6"/>
+      <c r="C48" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" t="s">
+        <v>92</v>
+      </c>
+      <c r="E48" s="3">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="2:5">
-      <c r="B46">
+    <row r="49" customFormat="1" spans="2:5">
+      <c r="B49">
         <v>4007</v>
       </c>
-      <c r="C46" t="s">
-        <v>67</v>
-      </c>
-      <c r="D46" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="3">
-        <f t="shared" si="6"/>
+      <c r="C49" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="3">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="C47" s="3"/>
-      <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="2:5">
-      <c r="C48" s="3"/>
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="5:5">
-      <c r="E49" s="3"/>
     </row>
     <row r="50" spans="5:5">
       <c r="E50" s="3"/>
@@ -2090,18 +2797,18 @@
       <c r="E73" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="D1:V1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D1:V1">
       <formula1>"i18n"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="D3">
       <formula1>"int,bool,enum,double,string[],string,float,uint,short,Vector4,Vector2,Vector3Int,Vector3,Color,Color32,Vector3[],Vector2Int,int[],float[],bool[],double[],ushort,ulong,int[][],double[][],decimal,long,float[][],bool[][],Rect,Quaternion,DateTime,sbyte,char"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E3:V3" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" sqref="E3:V3">
       <formula1>"double,int,bool,string,float,enum,string[],uint,short,Vector2[],Vector3Int[],int4[],int4,Vector3Int,Vector3,Vector4[],Vector2,Vector4,Color,Color32,Vector2Int,Vector3[],Vector2Int[],Type,long[],bool[],int[],float[],double[],float[][],decimal,double[][]"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>